--- a/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="300">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T10:12:02+00:00</t>
+    <t>2025-01-28T14:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,7 +514,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -533,7 +533,7 @@
     <t>HealthcareService.offeredIn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -594,10 +594,10 @@
     <t>The specific type of service that may be delivered or performed.</t>
   </si>
   <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -1258,7 +1258,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="28.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="102.765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1273,7 +1273,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.19921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.93359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3020,11 +3020,9 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y16" t="s" s="2">
         <v>185</v>
       </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
         <v>186</v>
       </c>
